--- a/files/蓝桥杯大赛报名和获奖情况统计表.xlsx
+++ b/files/蓝桥杯大赛报名和获奖情况统计表.xlsx
@@ -384,7 +384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -406,7 +406,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2122,10 +2125,18 @@
       <c r="F50" s="1">
         <v>2</v>
       </c>
-      <c r="G50" s="7"/>
-      <c r="H50" s="5"/>
-      <c r="I50" s="5"/>
-      <c r="J50" s="5"/>
+      <c r="G50" s="7">
+        <v>1</v>
+      </c>
+      <c r="H50" s="8">
+        <v>0</v>
+      </c>
+      <c r="I50" s="8">
+        <v>1</v>
+      </c>
+      <c r="J50" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
@@ -2150,7 +2161,7 @@
       </c>
       <c r="G51" s="1">
         <f t="shared" ref="G51" si="14">G50</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="1">
         <f t="shared" ref="H51" si="15">H50</f>
@@ -2158,7 +2169,7 @@
       </c>
       <c r="I51" s="1">
         <f t="shared" ref="I51" si="16">I50</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="1">
         <f t="shared" ref="J51" si="17">J50</f>

--- a/files/蓝桥杯大赛报名和获奖情况统计表.xlsx
+++ b/files/蓝桥杯大赛报名和获奖情况统计表.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="70">
   <si>
     <t>报名</t>
   </si>
@@ -297,12 +297,23 @@
     <t>工业产品设计</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>大学组</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获奖总数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0_ "/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +338,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -384,7 +404,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -410,6 +430,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -692,11 +739,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.58203125" customWidth="1"/>
-    <col min="2" max="10" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" customWidth="1"/>
+    <col min="3" max="3" width="10.58203125" style="14" customWidth="1"/>
+    <col min="4" max="10" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -706,7 +755,7 @@
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -738,7 +787,7 @@
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="11">
         <v>867</v>
       </c>
       <c r="D2" s="1">
@@ -770,7 +819,7 @@
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="11">
         <v>8</v>
       </c>
       <c r="D3" s="1">
@@ -802,7 +851,7 @@
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="11">
         <v>26</v>
       </c>
       <c r="D4" s="1">
@@ -834,7 +883,7 @@
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="11">
         <v>2</v>
       </c>
       <c r="D5" s="1">
@@ -866,7 +915,7 @@
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="11">
         <v>131</v>
       </c>
       <c r="D6" s="1">
@@ -898,7 +947,7 @@
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="11">
         <v>11</v>
       </c>
       <c r="D7" s="1">
@@ -930,7 +979,7 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="11">
         <v>6</v>
       </c>
       <c r="D8" s="1">
@@ -962,7 +1011,7 @@
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="11">
         <v>1</v>
       </c>
       <c r="D9" s="1">
@@ -992,7 +1041,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="1">
+      <c r="C10" s="11">
         <f>SUM(C2:C9)</f>
         <v>1052</v>
       </c>
@@ -1028,7 +1077,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="C11" s="11"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1044,7 +1093,7 @@
       <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1076,7 +1125,7 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="11">
         <v>124</v>
       </c>
       <c r="D13" s="1">
@@ -1108,7 +1157,7 @@
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="11">
         <v>55</v>
       </c>
       <c r="D14" s="1">
@@ -1140,7 +1189,7 @@
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="11">
         <v>40</v>
       </c>
       <c r="D15" s="1">
@@ -1172,7 +1221,7 @@
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="11">
         <v>9</v>
       </c>
       <c r="D16" s="1">
@@ -1204,7 +1253,7 @@
       <c r="B17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="11">
         <v>0</v>
       </c>
       <c r="D17" s="1">
@@ -1236,7 +1285,7 @@
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="11">
         <v>2</v>
       </c>
       <c r="D18" s="1">
@@ -1266,7 +1315,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="1">
+      <c r="C19" s="11">
         <f>SUM(C13:C18)</f>
         <v>230</v>
       </c>
@@ -1302,7 +1351,7 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="C20" s="11"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1318,7 +1367,7 @@
       <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="11" t="s">
         <v>0</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1350,7 +1399,7 @@
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="11">
         <v>4</v>
       </c>
       <c r="D22" s="1">
@@ -1380,7 +1429,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="1">
+      <c r="C23" s="11">
         <f>C22</f>
         <v>4</v>
       </c>
@@ -1420,7 +1469,7 @@
       <c r="B25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="11" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1431,7 +1480,7 @@
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="12" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1442,7 +1491,7 @@
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1474,7 +1523,7 @@
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="11">
         <f>SUM(D30:F30)</f>
         <v>465</v>
       </c>
@@ -1508,7 +1557,7 @@
       <c r="B31" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="11">
         <f t="shared" ref="C31:C37" si="4">SUM(D31:F31)</f>
         <v>6</v>
       </c>
@@ -1542,7 +1591,7 @@
       <c r="B32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="11">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1576,7 +1625,7 @@
       <c r="B33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="11">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1610,7 +1659,7 @@
       <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="11">
         <f t="shared" si="4"/>
         <v>52</v>
       </c>
@@ -1644,7 +1693,7 @@
       <c r="B35" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="11">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1678,7 +1727,7 @@
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="11">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1712,7 +1761,7 @@
       <c r="B37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="11">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1744,7 +1793,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="1">
+      <c r="C38" s="11">
         <f t="shared" ref="C38:J38" si="5">SUM(C30:C37)</f>
         <v>541</v>
       </c>
@@ -1780,7 +1829,7 @@
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="11"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1795,7 +1844,7 @@
       <c r="B40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -1827,7 +1876,7 @@
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="11">
         <f t="shared" ref="C41:C46" si="6">SUM(D41:F41)</f>
         <v>58</v>
       </c>
@@ -1861,7 +1910,7 @@
       <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="11">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
@@ -1895,7 +1944,7 @@
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="11">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
@@ -1929,7 +1978,7 @@
       <c r="B44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="11">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -1963,7 +2012,7 @@
       <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -1997,7 +2046,7 @@
       <c r="B46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="11">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2029,7 +2078,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="1">
+      <c r="C47" s="11">
         <f t="shared" ref="C47:J47" si="9">SUM(C41:C46)</f>
         <v>117</v>
       </c>
@@ -2065,7 +2114,7 @@
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
+      <c r="C48" s="11"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2080,7 +2129,7 @@
       <c r="B49" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2109,10 +2158,10 @@
       <c r="A50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="1">
+      <c r="B50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="11">
         <f>SUM(D50:F50)</f>
         <v>4</v>
       </c>
@@ -2143,7 +2192,7 @@
         <v>10</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="1">
+      <c r="C51" s="11">
         <f t="shared" ref="C51" si="10">C50</f>
         <v>4</v>
       </c>
@@ -2183,7 +2232,7 @@
       <c r="B53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2213,7 +2262,7 @@
         <v>43</v>
       </c>
       <c r="B54" s="1"/>
-      <c r="C54" s="1">
+      <c r="C54" s="11">
         <f>SUM(D54:F54)</f>
         <v>0</v>
       </c>
@@ -2245,7 +2294,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="1">
+      <c r="C55" s="11">
         <f>SUM(D55:F55)</f>
         <v>8</v>
       </c>
@@ -2258,17 +2307,25 @@
       <c r="F55" s="1">
         <v>3</v>
       </c>
-      <c r="G55" s="4"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
+      <c r="G55" s="9">
+        <v>1</v>
+      </c>
+      <c r="H55" s="8">
+        <v>0</v>
+      </c>
+      <c r="I55" s="8">
+        <v>0</v>
+      </c>
+      <c r="J55" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B56" s="1"/>
-      <c r="C56" s="1">
+      <c r="C56" s="11">
         <f>SUM(D56:F56)</f>
         <v>1</v>
       </c>
@@ -2281,17 +2338,17 @@
       <c r="F56" s="1">
         <v>0</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56" s="10">
         <f>SUM(H56:J56)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="1">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
+      <c r="H56" s="10">
+        <v>0</v>
+      </c>
+      <c r="I56" s="10">
+        <v>0</v>
+      </c>
+      <c r="J56" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2300,7 +2357,7 @@
         <v>46</v>
       </c>
       <c r="B57" s="1"/>
-      <c r="C57" s="1">
+      <c r="C57" s="11">
         <f t="shared" ref="C57:C65" si="18">SUM(D57:F57)</f>
         <v>1</v>
       </c>
@@ -2313,17 +2370,17 @@
       <c r="F57" s="1">
         <v>0</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57" s="10">
         <f>SUM(H57:J57)</f>
         <v>0</v>
       </c>
-      <c r="H57" s="1">
-        <v>0</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1">
+      <c r="H57" s="10">
+        <v>0</v>
+      </c>
+      <c r="I57" s="10">
+        <v>0</v>
+      </c>
+      <c r="J57" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2332,7 +2389,7 @@
         <v>47</v>
       </c>
       <c r="B58" s="1"/>
-      <c r="C58" s="1">
+      <c r="C58" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -2345,17 +2402,17 @@
       <c r="F58" s="1">
         <v>0</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58" s="10">
         <f>SUM(H58:J58)</f>
         <v>0</v>
       </c>
-      <c r="H58" s="1">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
+      <c r="H58" s="10">
+        <v>0</v>
+      </c>
+      <c r="I58" s="10">
+        <v>0</v>
+      </c>
+      <c r="J58" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2364,7 +2421,7 @@
         <v>67</v>
       </c>
       <c r="B59" s="1"/>
-      <c r="C59" s="1">
+      <c r="C59" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
@@ -2377,17 +2434,17 @@
       <c r="F59" s="1">
         <v>0</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59" s="10">
         <f>SUM(H59:J59)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="1">
-        <v>0</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="1">
+      <c r="H59" s="10">
+        <v>0</v>
+      </c>
+      <c r="I59" s="10">
+        <v>0</v>
+      </c>
+      <c r="J59" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2396,7 +2453,7 @@
         <v>48</v>
       </c>
       <c r="B60" s="1"/>
-      <c r="C60" s="1">
+      <c r="C60" s="11">
         <f t="shared" si="18"/>
         <v>11</v>
       </c>
@@ -2409,17 +2466,25 @@
       <c r="F60" s="1">
         <v>4</v>
       </c>
-      <c r="G60" s="4"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
+      <c r="G60" s="9">
+        <v>3</v>
+      </c>
+      <c r="H60" s="8">
+        <v>0</v>
+      </c>
+      <c r="I60" s="8">
+        <v>0</v>
+      </c>
+      <c r="J60" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B61" s="1"/>
-      <c r="C61" s="1">
+      <c r="C61" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
@@ -2451,7 +2516,7 @@
         <v>54</v>
       </c>
       <c r="B62" s="1"/>
-      <c r="C62" s="1">
+      <c r="C62" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -2483,7 +2548,7 @@
         <v>55</v>
       </c>
       <c r="B63" s="1"/>
-      <c r="C63" s="1">
+      <c r="C63" s="11">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
@@ -2515,7 +2580,7 @@
         <v>50</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="1">
+      <c r="C64" s="11">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
@@ -2549,7 +2614,7 @@
       <c r="B65" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="11">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -2583,7 +2648,7 @@
       <c r="B66" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="6"/>
+      <c r="C66" s="13"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -2597,7 +2662,7 @@
         <v>51</v>
       </c>
       <c r="B67" s="1"/>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="12" t="s">
         <v>61</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -2628,7 +2693,7 @@
         <v>52</v>
       </c>
       <c r="B68" s="1"/>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="12" t="s">
         <v>61</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -2659,7 +2724,7 @@
         <v>53</v>
       </c>
       <c r="B69" s="1"/>
-      <c r="C69" s="1">
+      <c r="C69" s="11">
         <f t="shared" ref="C69" si="21">SUM(D69:F69)</f>
         <v>0</v>
       </c>
@@ -2691,7 +2756,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="1"/>
-      <c r="C70" s="1">
+      <c r="C70" s="11">
         <f>SUM(C54:C69)</f>
         <v>26</v>
       </c>
@@ -2709,7 +2774,7 @@
       </c>
       <c r="G70" s="1">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H70" s="1">
         <f t="shared" si="22"/>
@@ -2721,12 +2786,53 @@
       </c>
       <c r="J70" s="1">
         <f t="shared" si="22"/>
-        <v>3</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="16">
+        <f>C38+C47+C51+C70</f>
+        <v>688</v>
+      </c>
+      <c r="D72" s="16">
+        <f>D38+D47+D51+D70</f>
+        <v>139</v>
+      </c>
+      <c r="E72" s="16">
+        <f>E38+E47+E51+E70</f>
+        <v>240</v>
+      </c>
+      <c r="F72" s="16">
+        <f>F38+F47+F51+F70</f>
+        <v>309</v>
+      </c>
+      <c r="G72" s="16">
+        <f>G38+G47+G51+G70</f>
+        <v>91</v>
+      </c>
+      <c r="H72" s="16">
+        <f>H38+H47+H51+H70</f>
+        <v>11</v>
+      </c>
+      <c r="I72" s="16">
+        <f>I38+I47+I51+I70</f>
+        <v>30</v>
+      </c>
+      <c r="J72" s="16">
+        <f>J38+J47+J51+J70</f>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="C50 C55 C60" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/files/蓝桥杯大赛报名和获奖情况统计表.xlsx
+++ b/files/蓝桥杯大赛报名和获奖情况统计表.xlsx
@@ -355,7 +355,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -365,12 +365,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +398,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -415,15 +409,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -444,9 +429,6 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
@@ -457,6 +439,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -744,7 +729,7 @@
   <cols>
     <col min="1" max="1" width="20.58203125" customWidth="1"/>
     <col min="2" max="2" width="10.58203125" customWidth="1"/>
-    <col min="3" max="3" width="10.58203125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="10.58203125" style="10" customWidth="1"/>
     <col min="4" max="10" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -755,7 +740,7 @@
       <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -787,7 +772,7 @@
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="8">
         <v>867</v>
       </c>
       <c r="D2" s="1">
@@ -819,7 +804,7 @@
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>8</v>
       </c>
       <c r="D3" s="1">
@@ -851,7 +836,7 @@
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="8">
         <v>26</v>
       </c>
       <c r="D4" s="1">
@@ -883,7 +868,7 @@
       <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="8">
         <v>2</v>
       </c>
       <c r="D5" s="1">
@@ -915,7 +900,7 @@
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="8">
         <v>131</v>
       </c>
       <c r="D6" s="1">
@@ -947,7 +932,7 @@
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="8">
         <v>11</v>
       </c>
       <c r="D7" s="1">
@@ -979,7 +964,7 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="8">
         <v>6</v>
       </c>
       <c r="D8" s="1">
@@ -1011,7 +996,7 @@
       <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="8">
         <v>1</v>
       </c>
       <c r="D9" s="1">
@@ -1041,7 +1026,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="1"/>
-      <c r="C10" s="11">
+      <c r="C10" s="8">
         <f>SUM(C2:C9)</f>
         <v>1052</v>
       </c>
@@ -1077,7 +1062,7 @@
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="11"/>
+      <c r="C11" s="8"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -1093,7 +1078,7 @@
       <c r="B12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1125,7 +1110,7 @@
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="8">
         <v>124</v>
       </c>
       <c r="D13" s="1">
@@ -1157,7 +1142,7 @@
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="8">
         <v>55</v>
       </c>
       <c r="D14" s="1">
@@ -1189,7 +1174,7 @@
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="8">
         <v>40</v>
       </c>
       <c r="D15" s="1">
@@ -1221,7 +1206,7 @@
       <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="8">
         <v>9</v>
       </c>
       <c r="D16" s="1">
@@ -1253,7 +1238,7 @@
       <c r="B17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="8">
         <v>0</v>
       </c>
       <c r="D17" s="1">
@@ -1285,7 +1270,7 @@
       <c r="B18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="8">
         <v>2</v>
       </c>
       <c r="D18" s="1">
@@ -1315,7 +1300,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="1"/>
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <f>SUM(C13:C18)</f>
         <v>230</v>
       </c>
@@ -1351,7 +1336,7 @@
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-      <c r="C20" s="11"/>
+      <c r="C20" s="8"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
@@ -1367,7 +1352,7 @@
       <c r="B21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1399,7 +1384,7 @@
       <c r="B22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="8">
         <v>4</v>
       </c>
       <c r="D22" s="1">
@@ -1429,7 +1414,7 @@
         <v>10</v>
       </c>
       <c r="B23" s="1"/>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <f>C22</f>
         <v>4</v>
       </c>
@@ -1469,7 +1454,7 @@
       <c r="B25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="8" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1480,7 +1465,7 @@
       <c r="B26" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="9" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1491,7 +1476,7 @@
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1523,7 +1508,7 @@
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="8">
         <f>SUM(D30:F30)</f>
         <v>465</v>
       </c>
@@ -1557,7 +1542,7 @@
       <c r="B31" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="8">
         <f t="shared" ref="C31:C37" si="4">SUM(D31:F31)</f>
         <v>6</v>
       </c>
@@ -1591,7 +1576,7 @@
       <c r="B32" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="8">
         <f t="shared" si="4"/>
         <v>12</v>
       </c>
@@ -1625,7 +1610,7 @@
       <c r="B33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1659,7 +1644,7 @@
       <c r="B34" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C34" s="8">
         <f t="shared" si="4"/>
         <v>52</v>
       </c>
@@ -1693,7 +1678,7 @@
       <c r="B35" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1727,7 +1712,7 @@
       <c r="B36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="8">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
@@ -1761,7 +1746,7 @@
       <c r="B37" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="8">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -1793,7 +1778,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="1"/>
-      <c r="C38" s="11">
+      <c r="C38" s="8">
         <f t="shared" ref="C38:J38" si="5">SUM(C30:C37)</f>
         <v>541</v>
       </c>
@@ -1829,7 +1814,7 @@
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-      <c r="C39" s="11"/>
+      <c r="C39" s="8"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -1844,7 +1829,7 @@
       <c r="B40" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -1876,7 +1861,7 @@
       <c r="B41" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="8">
         <f t="shared" ref="C41:C46" si="6">SUM(D41:F41)</f>
         <v>58</v>
       </c>
@@ -1910,7 +1895,7 @@
       <c r="B42" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C42" s="11">
+      <c r="C42" s="8">
         <f t="shared" si="6"/>
         <v>31</v>
       </c>
@@ -1944,7 +1929,7 @@
       <c r="B43" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="8">
         <f t="shared" si="6"/>
         <v>27</v>
       </c>
@@ -1978,7 +1963,7 @@
       <c r="B44" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="8">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
@@ -2012,7 +1997,7 @@
       <c r="B45" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2046,7 +2031,7 @@
       <c r="B46" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C46" s="11">
+      <c r="C46" s="8">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
@@ -2078,7 +2063,7 @@
         <v>10</v>
       </c>
       <c r="B47" s="1"/>
-      <c r="C47" s="11">
+      <c r="C47" s="8">
         <f t="shared" ref="C47:J47" si="9">SUM(C41:C46)</f>
         <v>117</v>
       </c>
@@ -2114,7 +2099,7 @@
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="11"/>
+      <c r="C48" s="8"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -2129,7 +2114,7 @@
       <c r="B49" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2161,7 +2146,7 @@
       <c r="B50" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="11">
+      <c r="C50" s="8">
         <f>SUM(D50:F50)</f>
         <v>4</v>
       </c>
@@ -2174,16 +2159,16 @@
       <c r="F50" s="1">
         <v>2</v>
       </c>
-      <c r="G50" s="7">
-        <v>1</v>
-      </c>
-      <c r="H50" s="8">
-        <v>0</v>
-      </c>
-      <c r="I50" s="8">
-        <v>1</v>
-      </c>
-      <c r="J50" s="8">
+      <c r="G50" s="4">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0</v>
+      </c>
+      <c r="I50" s="5">
+        <v>1</v>
+      </c>
+      <c r="J50" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2192,7 +2177,7 @@
         <v>10</v>
       </c>
       <c r="B51" s="1"/>
-      <c r="C51" s="11">
+      <c r="C51" s="8">
         <f t="shared" ref="C51" si="10">C50</f>
         <v>4</v>
       </c>
@@ -2232,7 +2217,7 @@
       <c r="B53" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2262,7 +2247,7 @@
         <v>43</v>
       </c>
       <c r="B54" s="1"/>
-      <c r="C54" s="11">
+      <c r="C54" s="8">
         <f>SUM(D54:F54)</f>
         <v>0</v>
       </c>
@@ -2294,7 +2279,7 @@
         <v>44</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="11">
+      <c r="C55" s="8">
         <f>SUM(D55:F55)</f>
         <v>8</v>
       </c>
@@ -2307,16 +2292,16 @@
       <c r="F55" s="1">
         <v>3</v>
       </c>
-      <c r="G55" s="9">
-        <v>1</v>
-      </c>
-      <c r="H55" s="8">
-        <v>0</v>
-      </c>
-      <c r="I55" s="8">
-        <v>0</v>
-      </c>
-      <c r="J55" s="8">
+      <c r="G55" s="6">
+        <v>1</v>
+      </c>
+      <c r="H55" s="5">
+        <v>0</v>
+      </c>
+      <c r="I55" s="5">
+        <v>0</v>
+      </c>
+      <c r="J55" s="5">
         <v>1</v>
       </c>
     </row>
@@ -2325,7 +2310,7 @@
         <v>45</v>
       </c>
       <c r="B56" s="1"/>
-      <c r="C56" s="11">
+      <c r="C56" s="8">
         <f>SUM(D56:F56)</f>
         <v>1</v>
       </c>
@@ -2338,17 +2323,17 @@
       <c r="F56" s="1">
         <v>0</v>
       </c>
-      <c r="G56" s="10">
+      <c r="G56" s="7">
         <f>SUM(H56:J56)</f>
         <v>0</v>
       </c>
-      <c r="H56" s="10">
-        <v>0</v>
-      </c>
-      <c r="I56" s="10">
-        <v>0</v>
-      </c>
-      <c r="J56" s="10">
+      <c r="H56" s="7">
+        <v>0</v>
+      </c>
+      <c r="I56" s="7">
+        <v>0</v>
+      </c>
+      <c r="J56" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2357,7 +2342,7 @@
         <v>46</v>
       </c>
       <c r="B57" s="1"/>
-      <c r="C57" s="11">
+      <c r="C57" s="8">
         <f t="shared" ref="C57:C65" si="18">SUM(D57:F57)</f>
         <v>1</v>
       </c>
@@ -2370,17 +2355,17 @@
       <c r="F57" s="1">
         <v>0</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="7">
         <f>SUM(H57:J57)</f>
         <v>0</v>
       </c>
-      <c r="H57" s="10">
-        <v>0</v>
-      </c>
-      <c r="I57" s="10">
-        <v>0</v>
-      </c>
-      <c r="J57" s="10">
+      <c r="H57" s="7">
+        <v>0</v>
+      </c>
+      <c r="I57" s="7">
+        <v>0</v>
+      </c>
+      <c r="J57" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2389,7 +2374,7 @@
         <v>47</v>
       </c>
       <c r="B58" s="1"/>
-      <c r="C58" s="11">
+      <c r="C58" s="8">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -2402,17 +2387,17 @@
       <c r="F58" s="1">
         <v>0</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="7">
         <f>SUM(H58:J58)</f>
         <v>0</v>
       </c>
-      <c r="H58" s="10">
-        <v>0</v>
-      </c>
-      <c r="I58" s="10">
-        <v>0</v>
-      </c>
-      <c r="J58" s="10">
+      <c r="H58" s="7">
+        <v>0</v>
+      </c>
+      <c r="I58" s="7">
+        <v>0</v>
+      </c>
+      <c r="J58" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2421,7 +2406,7 @@
         <v>67</v>
       </c>
       <c r="B59" s="1"/>
-      <c r="C59" s="11">
+      <c r="C59" s="8">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
@@ -2434,17 +2419,17 @@
       <c r="F59" s="1">
         <v>0</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59" s="7">
         <f>SUM(H59:J59)</f>
         <v>0</v>
       </c>
-      <c r="H59" s="10">
-        <v>0</v>
-      </c>
-      <c r="I59" s="10">
-        <v>0</v>
-      </c>
-      <c r="J59" s="10">
+      <c r="H59" s="7">
+        <v>0</v>
+      </c>
+      <c r="I59" s="7">
+        <v>0</v>
+      </c>
+      <c r="J59" s="7">
         <v>0</v>
       </c>
     </row>
@@ -2453,7 +2438,7 @@
         <v>48</v>
       </c>
       <c r="B60" s="1"/>
-      <c r="C60" s="11">
+      <c r="C60" s="8">
         <f t="shared" si="18"/>
         <v>11</v>
       </c>
@@ -2466,16 +2451,16 @@
       <c r="F60" s="1">
         <v>4</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="6">
         <v>3</v>
       </c>
-      <c r="H60" s="8">
-        <v>0</v>
-      </c>
-      <c r="I60" s="8">
-        <v>0</v>
-      </c>
-      <c r="J60" s="8">
+      <c r="H60" s="5">
+        <v>0</v>
+      </c>
+      <c r="I60" s="5">
+        <v>0</v>
+      </c>
+      <c r="J60" s="5">
         <v>3</v>
       </c>
     </row>
@@ -2484,7 +2469,7 @@
         <v>49</v>
       </c>
       <c r="B61" s="1"/>
-      <c r="C61" s="11">
+      <c r="C61" s="8">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
@@ -2516,7 +2501,7 @@
         <v>54</v>
       </c>
       <c r="B62" s="1"/>
-      <c r="C62" s="11">
+      <c r="C62" s="8">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -2548,7 +2533,7 @@
         <v>55</v>
       </c>
       <c r="B63" s="1"/>
-      <c r="C63" s="11">
+      <c r="C63" s="8">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
@@ -2580,7 +2565,7 @@
         <v>50</v>
       </c>
       <c r="B64" s="1"/>
-      <c r="C64" s="11">
+      <c r="C64" s="8">
         <f t="shared" si="18"/>
         <v>1</v>
       </c>
@@ -2614,7 +2599,7 @@
       <c r="B65" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="8">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
@@ -2648,21 +2633,37 @@
       <c r="B66" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C66" s="13"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
+      <c r="C66" s="14">
+        <v>0</v>
+      </c>
+      <c r="D66" s="7">
+        <v>0</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0</v>
+      </c>
+      <c r="F66" s="7">
+        <v>0</v>
+      </c>
+      <c r="G66" s="6">
+        <v>0</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0</v>
+      </c>
+      <c r="I66" s="5">
+        <v>0</v>
+      </c>
+      <c r="J66" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B67" s="1"/>
-      <c r="C67" s="12" t="s">
+      <c r="C67" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D67" s="2" t="s">
@@ -2693,7 +2694,7 @@
         <v>52</v>
       </c>
       <c r="B68" s="1"/>
-      <c r="C68" s="12" t="s">
+      <c r="C68" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D68" s="2" t="s">
@@ -2724,7 +2725,7 @@
         <v>53</v>
       </c>
       <c r="B69" s="1"/>
-      <c r="C69" s="11">
+      <c r="C69" s="8">
         <f t="shared" ref="C69" si="21">SUM(D69:F69)</f>
         <v>0</v>
       </c>
@@ -2756,7 +2757,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="1"/>
-      <c r="C70" s="11">
+      <c r="C70" s="8">
         <f>SUM(C54:C69)</f>
         <v>26</v>
       </c>
@@ -2790,40 +2791,40 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B72" s="15"/>
-      <c r="C72" s="16">
-        <f>C38+C47+C51+C70</f>
+      <c r="B72" s="11"/>
+      <c r="C72" s="12">
+        <f t="shared" ref="C72:J72" si="23">C38+C47+C51+C70</f>
         <v>688</v>
       </c>
-      <c r="D72" s="16">
-        <f>D38+D47+D51+D70</f>
+      <c r="D72" s="12">
+        <f t="shared" si="23"/>
         <v>139</v>
       </c>
-      <c r="E72" s="16">
-        <f>E38+E47+E51+E70</f>
+      <c r="E72" s="12">
+        <f t="shared" si="23"/>
         <v>240</v>
       </c>
-      <c r="F72" s="16">
-        <f>F38+F47+F51+F70</f>
+      <c r="F72" s="12">
+        <f t="shared" si="23"/>
         <v>309</v>
       </c>
-      <c r="G72" s="16">
-        <f>G38+G47+G51+G70</f>
+      <c r="G72" s="12">
+        <f t="shared" si="23"/>
         <v>91</v>
       </c>
-      <c r="H72" s="16">
-        <f>H38+H47+H51+H70</f>
+      <c r="H72" s="12">
+        <f t="shared" si="23"/>
         <v>11</v>
       </c>
-      <c r="I72" s="16">
-        <f>I38+I47+I51+I70</f>
+      <c r="I72" s="12">
+        <f t="shared" si="23"/>
         <v>30</v>
       </c>
-      <c r="J72" s="16">
-        <f>J38+J47+J51+J70</f>
+      <c r="J72" s="12">
+        <f t="shared" si="23"/>
         <v>50</v>
       </c>
     </row>
